--- a/TESTING/src/test/resources/testdata/UI_ProductData.xlsx
+++ b/TESTING/src/test/resources/testdata/UI_ProductData.xlsx
@@ -7,12 +7,15 @@
   </bookViews>
   <sheets>
     <sheet name="SearchUI" r:id="rId3" sheetId="1"/>
+    <sheet name="AIListing" r:id="rId4" sheetId="2"/>
+    <sheet name="SellerUpload" r:id="rId5" sheetId="3"/>
+    <sheet name="ImageUpload" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="80">
   <si>
     <t>TestCaseId</t>
   </si>
@@ -51,6 +54,207 @@
   </si>
   <si>
     <t>Second valid keyword</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>DeliveryOption</t>
+  </si>
+  <si>
+    <t>ReturnOption</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>TC031</t>
+  </si>
+  <si>
+    <t>GENERATE</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Home Delivery</t>
+  </si>
+  <si>
+    <t>No Returns</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>AI content generation</t>
+  </si>
+  <si>
+    <t>TC032</t>
+  </si>
+  <si>
+    <t>Tag generation 5-10 tags</t>
+  </si>
+  <si>
+    <t>TC033</t>
+  </si>
+  <si>
+    <t>Category auto-assign</t>
+  </si>
+  <si>
+    <t>TC034</t>
+  </si>
+  <si>
+    <t>Highlights 3-5</t>
+  </si>
+  <si>
+    <t>TC035</t>
+  </si>
+  <si>
+    <t>Preview display</t>
+  </si>
+  <si>
+    <t>TC036</t>
+  </si>
+  <si>
+    <t>EDIT</t>
+  </si>
+  <si>
+    <t>Premium Basmati Rice 1kg</t>
+  </si>
+  <si>
+    <t>299</t>
+  </si>
+  <si>
+    <t>Edit listing after AI generation</t>
+  </si>
+  <si>
+    <t>TC037</t>
+  </si>
+  <si>
+    <t>PUBLISH</t>
+  </si>
+  <si>
+    <t>Publish listing</t>
+  </si>
+  <si>
+    <t>TC038</t>
+  </si>
+  <si>
+    <t>E2E</t>
+  </si>
+  <si>
+    <t>End-to-end pipeline timing</t>
+  </si>
+  <si>
+    <t>TitlePrefix</t>
+  </si>
+  <si>
+    <t>ProductDescription</t>
+  </si>
+  <si>
+    <t>TC020</t>
+  </si>
+  <si>
+    <t>CREATE</t>
+  </si>
+  <si>
+    <t>UI Test Rice</t>
+  </si>
+  <si>
+    <t>1 kg pack, organic</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>Seller creates a product listing</t>
+  </si>
+  <si>
+    <t>TC028</t>
+  </si>
+  <si>
+    <t>FORM_FIELDS</t>
+  </si>
+  <si>
+    <t>Smoke Title</t>
+  </si>
+  <si>
+    <t>Smoke description text for automated test</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>Seller upload form fields present</t>
+  </si>
+  <si>
+    <t>Format</t>
+  </si>
+  <si>
+    <t>Width</t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>SizeMB</t>
+  </si>
+  <si>
+    <t>TC025</t>
+  </si>
+  <si>
+    <t>VALID_JPEG</t>
+  </si>
+  <si>
+    <t>jpg</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Valid JPEG within size limit</t>
+  </si>
+  <si>
+    <t>TC026</t>
+  </si>
+  <si>
+    <t>INVALID_TYPE</t>
+  </si>
+  <si>
+    <t>pdf</t>
+  </si>
+  <si>
+    <t>Reject non-image type (PDF)</t>
+  </si>
+  <si>
+    <t>TC027</t>
+  </si>
+  <si>
+    <t>OVERSIZED</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Reject file size exceeding 10MB</t>
+  </si>
+  <si>
+    <t>VALID_PNG</t>
+  </si>
+  <si>
+    <t>png</t>
+  </si>
+  <si>
+    <t>Valid PNG within size limit</t>
   </si>
 </sst>
 </file>
@@ -152,4 +356,452 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>